--- a/InputData/trans/AVOP/Avg Veh Ownership Period.xlsx
+++ b/InputData/trans/AVOP/Avg Veh Ownership Period.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/My Drive/2024/FO local_EPS ICM/Diario/20250206_Flota/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\Mexico\Models\eps-mexico\InputData\trans\AVOP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{46546555-91C5-0041-8F22-5333CF10175B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAB2AFA7-3991-4FAD-A829-4439E8DE0AC9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6A9B84-E4B8-4FB0-812F-D347F94F1C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3140" yWindow="-21100" windowWidth="33600" windowHeight="20500" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>AVOP Average Vehicle Ownership Period</t>
   </si>
@@ -114,9 +114,6 @@
     <t>Notes:</t>
   </si>
   <si>
-    <t>We use the same data as for Average Vehicle Lifetime, and an assumptions of number of owners</t>
-  </si>
-  <si>
     <t>MEXICO</t>
   </si>
   <si>
@@ -157,6 +154,24 @@
   </si>
   <si>
     <t>freight</t>
+  </si>
+  <si>
+    <t>Freight LDVs and HDVs</t>
+  </si>
+  <si>
+    <t>International Council on Clean Transportation</t>
+  </si>
+  <si>
+    <t>https://theicct.org/wp-content/uploads/2021/06/Mexico-freight-assessment_ICCT-Consultant-Report_Oct2017.pdf</t>
+  </si>
+  <si>
+    <t>Mexico Freight Assessment</t>
+  </si>
+  <si>
+    <t>We use the same data as for Average Vehicle Lifetime, and an assumptions of number of owners, except for onroad freight</t>
+  </si>
+  <si>
+    <t>p.53</t>
   </si>
 </sst>
 </file>
@@ -1599,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -1675,67 +1690,98 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="2:2">
       <c r="B17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="2:2">
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="2:2">
       <c r="B19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="2:2">
       <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="2:2">
       <c r="B22" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="2:2">
       <c r="B23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="2:2">
       <c r="B24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="2:2">
       <c r="B25" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="2:2">
       <c r="B26" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="2:2">
+      <c r="B28" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="2">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="B33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>21</v>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B25" r:id="rId1" xr:uid="{D8F5C839-1F3D-476B-8CF3-68EA878EF9CA}"/>
+    <hyperlink ref="B32" r:id="rId2" xr:uid="{D6BED324-C0E7-48E7-9378-2BBD9DE5BEE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1746,38 +1792,38 @@
   <sheetData>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="48">
-      <c r="A3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
       <c r="F3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>24</v>
@@ -1789,7 +1835,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" s="12">
         <v>17</v>
@@ -1800,7 +1846,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="13">
         <v>25</v>
@@ -1812,7 +1858,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" s="12">
         <v>12</v>
@@ -1846,7 +1892,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>45</v>
@@ -1858,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" s="12">
         <v>34</v>
@@ -1869,7 +1915,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>44</v>
@@ -1881,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="12">
         <v>33</v>
@@ -1892,7 +1938,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9">
         <v>11</v>
@@ -1904,7 +1950,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" s="12">
         <v>17</v>
@@ -1930,15 +1976,15 @@
     <col min="2" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="48">
+    <row r="1" spans="1:37" ht="60">
       <c r="A1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="1"/>
@@ -1977,15 +2023,14 @@
     </row>
     <row r="2" spans="1:37">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="7">
         <f>ROUND(AVL!B4/AVL!$D4,0)</f>
         <v>8</v>
       </c>
-      <c r="C2" s="7">
-        <f>ROUND(AVL!C4/AVL!$D4,0)</f>
-        <v>8</v>
+      <c r="C2" s="14">
+        <v>5</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2024,15 +2069,14 @@
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="7">
         <f>ROUND(AVL!B5/AVL!$D5,0)</f>
         <v>13</v>
       </c>
-      <c r="C3" s="7">
-        <f>ROUND(AVL!C5/AVL!$D5,0)</f>
-        <v>17</v>
+      <c r="C3" s="14">
+        <v>5</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2118,7 +2162,7 @@
     </row>
     <row r="5" spans="1:37">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="7">
         <f>ROUND(AVL!B7/AVL!$D7,0)</f>
@@ -2165,7 +2209,7 @@
     </row>
     <row r="6" spans="1:37">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="7">
         <f>ROUND(AVL!B8/AVL!$D8,0)</f>
@@ -2212,7 +2256,7 @@
     </row>
     <row r="7" spans="1:37">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="14">
         <f>ROUND(AVL!B9/AVL!$D9,0)</f>
@@ -2422,13 +2466,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78F1F79C-2571-4802-B485-05A4491151A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78F1F79C-2571-4802-B485-05A4491151A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0E317E3-51F2-41AC-B8D0-96B353FF6EA1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0E317E3-51F2-41AC-B8D0-96B353FF6EA1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FF3F324-0775-4003-BF60-A444A7FE0CFD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FF3F324-0775-4003-BF60-A444A7FE0CFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>